--- a/notion_pm/docs/template-development-wbs.xlsx
+++ b/notion_pm/docs/template-development-wbs.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="125">
   <si>
     <t>template-development summary</t>
   </si>
@@ -75,10 +75,10 @@
     <t>ID</t>
   </si>
   <si>
-    <t>工程(自動)</t>
+    <t>工程(親タスク)</t>
   </si>
   <si>
-    <t>タスク</t>
+    <t>タスク(子タスク)</t>
   </si>
   <si>
     <t>大項目</t>
@@ -312,7 +312,7 @@
     <t>ID接頭辞</t>
   </si>
   <si>
-    <t>工程</t>
+    <t>タスク</t>
   </si>
   <si>
     <t>開始日</t>
@@ -385,6 +385,9 @@
   </si>
   <si>
     <t>勤労感謝の日</t>
+  </si>
+  <si>
+    <t>工程</t>
   </si>
   <si>
     <t>日数</t>
@@ -37168,10 +37171,10 @@
         <v>97</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2">
